--- a/Result/checksun_type/稜鏡片.xlsx
+++ b/Result/checksun_type/稜鏡片.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>32.16</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>34.99</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>34.99</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>5050.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4336.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4336.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5777.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>6847.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>6847</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-351.2719648777975</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>5050</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>5050.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>31.72</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>32.68</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>35.1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>5616.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4001.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4001.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5931.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7423.62</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7423.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-411.2842611585756</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>5616</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>5616.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>31.46</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>35.26</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>35.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2561.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3993.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3993</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>5845.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7707.14</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7707.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-542.9702465183082</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2561</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2561.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>31.64</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>35.47</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>35.47</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>4686.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4282.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>4282.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5931.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7956.74</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7956.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-384.3798596565584</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>4686</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4686.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>31.98</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>33.08</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>35.68</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>35.68</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>3769.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4989.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>4989.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5806.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>8223.9</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>8223.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-371.7728834377531</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>3769</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>3769.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>33.24</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>35.88</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>35.88</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3377.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>7218.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>7218.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>6107.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>8475.5</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>8475.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-242.23531443097</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3377</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3377.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>32.85</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.42</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>36.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>5572.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7861.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7861.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>6235.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>9406.68</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>9406.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-6.530383191601686</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>5572</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5572.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>33.15</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.56</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>36.32</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>36.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>4007.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>7697.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>7697.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>6678.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>11379.82</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>11379.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>95.24560369291066</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>4007</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>4007.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>33.18</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>36.47</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>36.47</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>8221.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>7579.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>7579.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>6844.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>11648.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>11648.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>404.9168133960384</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>8221</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>8221.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>33.13</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>33.78</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>14915.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>6624.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>6624.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>6226.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>12140.42</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>12140.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>381.3429410649342</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>14915</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>14915.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>32.96999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>33.82</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>36.81</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>36.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>6591.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4996.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4996.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>5294.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>15620.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>15620.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-383.1676958746775</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>6591</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>6591.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>58.94</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>60.02</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>60.28</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>60.28</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>15324.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>8129.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>8129.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>10980.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>12247.68</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>12247.68</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1338.613092087846</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>15324</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>15324.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>58.14</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>60.16</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>60.27</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>60.16</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>60.27</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>4164.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>8620.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>8620.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>9990.2</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>12554.58</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>12554.58</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-2000.954018343326</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>4164</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>4164.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>57.84</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>60.34</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>60.33</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>60.34</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>60.33</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2830.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>10935.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>10935.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>10513.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>12697.8</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>12697.8</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-1679.978412338893</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2830</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2830.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>57.64</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>60.54</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>60.4</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>8163.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>13385.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>13385.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>13276.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>13310.96</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>13310.96</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-1018.514031891889</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>8163</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>8163.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>57.77999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>60.74</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>60.51</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>60.74</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>60.51</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>10168.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>13264.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>13264.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>13622.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>13357.1</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>13357.1</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-608.5822729714582</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>10168</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>10168.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>58.02</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>60.95</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>60.64</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>60.64</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>17777.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>13832.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>13832</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>14882.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>13432.18</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>13432.18</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-216.0518219075748</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>17777</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>17777.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>58.48</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>60.81</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>60.81</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>15738.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>11360.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>11360</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>20395.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>13766.46</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>13766.46</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-462.827898176758</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>15738</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>15738.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>58.58</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>61.37</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>60.93</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>60.93</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>15081.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>10090.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>10090.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>21757.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>13684.76</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>13684.76</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-580.3712964835631</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>15081</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>15081.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>58.7</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>61.55</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>61.03</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>61.03</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>7560.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>13167.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>13167.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>21748.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>13595.16</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>13595.16</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-657.1700334760171</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>7560</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>7560.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>59.22000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>61.66</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>61.1</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>61.66</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>61.1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>13004.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>13980.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>13980.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>21782.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>13721.16</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>13721.16</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>62.40927201605155</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>13004</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>13004.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>59.72000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>61.69</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>61.18</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>61.69</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>61.18</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>5417.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>15932.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>15932</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>21818.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>13767.98</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>13767.98</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>504.8650915755788</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>5417</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>5417.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10463,11 +10331,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>3666</t>
@@ -10649,41 +10513,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr">
         <is>
           <t>0</t>
@@ -10704,20 +10564,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>0</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10590,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>0</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10759,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10943,11 @@
           <t>18.02</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>17.34</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>17.84</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>17.84</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10994,16 @@
           <t>22.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>41.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>172.9</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11020,10 @@
           <t>-30.09928021989141</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>22</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11189,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11373,11 @@
           <t>18.22</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>17.31</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>17.85</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>17.85</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11424,16 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>74.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>74.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>197.8</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11450,10 @@
           <t>-25.2129541014458</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>2</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11619,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11803,11 @@
           <t>18.29</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>17.29</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>17.81</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>17.81</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11854,16 @@
           <t>159.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>131.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>131.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>224.2</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11880,10 @@
           <t>-15.18916842861469</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>159</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12049,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12233,11 @@
           <t>18.35</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>17.28</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>17.78</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>17.78</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12284,16 @@
           <t>4.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>169.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>169.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>222.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12310,10 @@
           <t>-17.14843288069119</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>4</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12479,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12663,11 @@
           <t>18.23</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>17.24</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>17.74</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>17.74</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12714,16 @@
           <t>22.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>237.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>237.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>229.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12740,10 @@
           <t>-2.727795209347221</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>22</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12909,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13093,11 @@
           <t>18.13</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>17.2</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>17.7</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>17.7</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13144,16 @@
           <t>187.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>304.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>304</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>234.2</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13170,10 @@
           <t>16.04196557862085</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>187</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>187.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13339,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13523,11 @@
           <t>17.88</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>17.16</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>17.66</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13574,16 @@
           <t>285.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>320.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>320.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>217.1</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13600,10 @@
           <t>24.60441079076736</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>285</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>285.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13769,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13953,11 @@
           <t>17.62</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>17.12</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>17.63</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>17.63</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14004,16 @@
           <t>348.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>317.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>317</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>198.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14030,10 @@
           <t>25.457746422735</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>348</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>348.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14199,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14383,11 @@
           <t>17.32</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>17.59</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>17.59</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14434,16 @@
           <t>344.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>276.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>276.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>178.6</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14460,10 @@
           <t>19.0175920961625</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>344</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>344.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14629,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14813,11 @@
           <t>17.0</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>17.09</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>17.57</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>17.57</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14864,16 @@
           <t>356.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>221.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>221.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>150.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14890,10 @@
           <t>9.566743340481736</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>356</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>356.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15059,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15243,11 @@
           <t>16.72</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>17.06</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>17.53</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>17.53</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15294,16 @@
           <t>271.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>164.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>164.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>128.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15320,10 @@
           <t>-5.561852858365171</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>271</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>271.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15489,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15673,11 @@
           <t>48.59</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>55.94</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>55.94</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15724,16 @@
           <t>4169372.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>5775453.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>5775453.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>8176625.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>24458409.56</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>24458409.56</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15750,10 @@
           <t>-2744556.420795419</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>4169372</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>4169372.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15919,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16103,11 @@
           <t>48.42</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>51.52</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>56.14</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>56.14</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16154,16 @@
           <t>2942740.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>6756179.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>6756179</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>8877554.2</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>24843448.68</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>24843448.68</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16180,10 @@
           <t>-2790711.43240849</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>2942740</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>2942740.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16349,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16533,11 @@
           <t>48.53</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>51.88</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>56.39</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>56.39</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16584,16 @@
           <t>7864161.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>7976679.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>7976679.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>9385728.2</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>25482271.3</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>25482271.3</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16610,10 @@
           <t>-2625554.040698288</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>7864161</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>7864161.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16779,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16963,11 @@
           <t>48.79</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>52.33</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>56.62</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>56.62</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17014,16 @@
           <t>8504637.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>8478713.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>8478713</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>9154921.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>25798547.78</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>25798547.78</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17040,10 @@
           <t>-2823140.229658773</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>8504637</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>8504637.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17209,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17393,11 @@
           <t>49.50000000000001</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>52.82</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>56.89</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>52.82</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>56.89</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17444,16 @@
           <t>5396358.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>8627001.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>8627001</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>9068652.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>26072897.42</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>26072897.42</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17470,10 @@
           <t>-3073202.20568594</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>5396358</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>5396358.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17639,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17823,11 @@
           <t>50.13000000000001</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>53.39</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>57.14</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>53.39</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>57.14</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17874,16 @@
           <t>9072999.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>10577796.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>10577796.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>10475644.5</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>26406367.76</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>26406367.76</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17900,10 @@
           <t>-2987646.48552168</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>9072999</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>9072999.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18069,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18253,11 @@
           <t>50.95</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>53.94</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>57.38</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>57.38</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18304,16 @@
           <t>9045242.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>10998929.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>10998929.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>11459108.7</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>27622118.22</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>27622118.22</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18330,10 @@
           <t>-3152648.189375535</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>9045242</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>9045242.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18499,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18683,11 @@
           <t>51.47000000000001</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>54.38</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>57.64</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>57.64</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18734,16 @@
           <t>10374329.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>10794777.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>10794777</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>12191735.9</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>30274998.3</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>30274998.3</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18760,10 @@
           <t>-3272796.36668906</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>10374329</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>10374329.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18929,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19113,11 @@
           <t>51.9</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>54.72</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>57.81</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>57.81</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19164,16 @@
           <t>9246077.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>9831130.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>9831130.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>13003175.9</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>30478161.18</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>30478161.18</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19190,10 @@
           <t>-3469953.214040915</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>9246077</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>9246077.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19359,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19543,11 @@
           <t>52.04</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>57.95</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>57.95</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19594,16 @@
           <t>15150337.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>9510304.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>9510304.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>13910257.6</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>30729831.82</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>30729831.82</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19620,10 @@
           <t>-3506794.809756389</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>15150337</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>15150337.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19789,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19973,11 @@
           <t>52.17999999999999</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>55.37</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>58.1</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20024,16 @@
           <t>11178662.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>10373492.2</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>10373492.2</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>14511147.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>30900423.04</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>30900423.04</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20050,10 @@
           <t>-4066782.274715764</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>11178662</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>11178662.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
